--- a/backend/dpd_.xlsx
+++ b/backend/dpd_.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEC6B6CB-BC04-4D43-AF9E-8B6F6BCC51CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4491E8B1-7DE5-4FAC-8B39-811E612E9E5B}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4448,7 +4448,7 @@
     <xf numFmtId="11" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>

--- a/backend/dpd_.xlsx
+++ b/backend/dpd_.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="334" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4491E8B1-7DE5-4FAC-8B39-811E612E9E5B}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{311FA273-38AC-4B3B-B75D-B8FDE4484B5D}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="1424">
   <si>
     <t>ACC</t>
   </si>
@@ -4276,6 +4276,33 @@
   </si>
   <si>
     <t>7d69dc80-c3e8-4899-a865-b9ec3c606d12</t>
+  </si>
+  <si>
+    <t>เนตรณรินทร์ ดอกพุฒ</t>
+  </si>
+  <si>
+    <t>0969251097</t>
+  </si>
+  <si>
+    <t>2fd3dc86-1f7f-4754-9296-808e9d9c06bb</t>
+  </si>
+  <si>
+    <t>ยศกร ภู่บึงพร้าว</t>
+  </si>
+  <si>
+    <t>0870777687</t>
+  </si>
+  <si>
+    <t>dec1cb14-2b3d-4f59-8483-dfaec14c920d</t>
+  </si>
+  <si>
+    <t>ชนายุส แสนมั่ง</t>
+  </si>
+  <si>
+    <t>0966750089</t>
+  </si>
+  <si>
+    <t>32023500-8bc3-4234-a088-2a38039ee9a2</t>
   </si>
 </sst>
 </file>
@@ -4448,7 +4475,7 @@
     <xf numFmtId="11" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
@@ -4951,8 +4978,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O352" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="A1:O352" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O355" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
+  <autoFilter ref="A1:O355" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
   <tableColumns count="15">
     <tableColumn id="2" xr3:uid="{8056A4BF-1F51-408D-984A-13A9B55C81C2}" name="ACC" dataDxfId="14"/>
     <tableColumn id="1" xr3:uid="{AFEB8EFF-C7CD-487F-8B94-1A5CF9E8D70C}" name="NAME" dataDxfId="13"/>
@@ -5271,7 +5298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O352"/>
+  <dimension ref="A1:O355"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -16687,6 +16714,75 @@
         <v>1414</v>
       </c>
     </row>
+    <row r="353" spans="1:15" ht="15">
+      <c r="A353" s="14"/>
+      <c r="B353" s="14" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C353" s="19" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D353" s="14"/>
+      <c r="E353" s="14"/>
+      <c r="F353" s="14"/>
+      <c r="G353" s="11"/>
+      <c r="H353" s="11"/>
+      <c r="I353" s="11"/>
+      <c r="J353" s="11"/>
+      <c r="K353" s="11"/>
+      <c r="L353" s="11"/>
+      <c r="M353" s="11"/>
+      <c r="N353" s="11"/>
+      <c r="O353" s="24" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15" ht="15">
+      <c r="A354" s="14"/>
+      <c r="B354" s="14" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C354" s="19" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D354" s="14"/>
+      <c r="E354" s="14"/>
+      <c r="F354" s="14"/>
+      <c r="G354" s="11"/>
+      <c r="H354" s="11"/>
+      <c r="I354" s="11"/>
+      <c r="J354" s="11"/>
+      <c r="K354" s="11"/>
+      <c r="L354" s="11"/>
+      <c r="M354" s="11"/>
+      <c r="N354" s="11"/>
+      <c r="O354" s="24" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="355" spans="1:15" ht="15">
+      <c r="A355" s="14"/>
+      <c r="B355" s="14" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C355" s="19" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D355" s="14"/>
+      <c r="E355" s="14"/>
+      <c r="F355" s="14"/>
+      <c r="G355" s="11"/>
+      <c r="H355" s="11"/>
+      <c r="I355" s="11"/>
+      <c r="J355" s="11"/>
+      <c r="K355" s="11"/>
+      <c r="L355" s="11"/>
+      <c r="M355" s="11"/>
+      <c r="N355" s="11"/>
+      <c r="O355" s="24" t="s">
+        <v>1423</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="17" priority="1"/>

--- a/backend/dpd_.xlsx
+++ b/backend/dpd_.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="440" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1F6152B-099B-46D5-B466-2EC1840F0C29}"/>
+  <xr:revisionPtr revIDLastSave="449" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D6210D-4C47-406C-BB73-EDEF876CCF3C}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="1482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="1488">
   <si>
     <t>ACC</t>
   </si>
@@ -4477,6 +4477,24 @@
   </si>
   <si>
     <t>0862909636</t>
+  </si>
+  <si>
+    <t>นางดรุณี สงวนรัษฎ์</t>
+  </si>
+  <si>
+    <t>0872063796</t>
+  </si>
+  <si>
+    <t>แฟนพี่อ้น</t>
+  </si>
+  <si>
+    <t>ภัคพงศ์ แพงผม</t>
+  </si>
+  <si>
+    <t>0892686198</t>
+  </si>
+  <si>
+    <t>พี่ดำ</t>
   </si>
 </sst>
 </file>
@@ -5152,8 +5170,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O385" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="A1:O385" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O387" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
+  <autoFilter ref="A1:O387" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
   <tableColumns count="15">
     <tableColumn id="2" xr3:uid="{8056A4BF-1F51-408D-984A-13A9B55C81C2}" name="ACC" dataDxfId="14"/>
     <tableColumn id="1" xr3:uid="{AFEB8EFF-C7CD-487F-8B94-1A5CF9E8D70C}" name="NAME" dataDxfId="13"/>
@@ -5472,7 +5490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O385"/>
+  <dimension ref="A1:O387"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -17603,6 +17621,52 @@
       <c r="N385" s="11"/>
       <c r="O385" s="11"/>
     </row>
+    <row r="386" spans="1:15" ht="15">
+      <c r="A386" s="14"/>
+      <c r="B386" s="14" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C386" s="19" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D386" s="14"/>
+      <c r="E386" s="14"/>
+      <c r="F386" s="14"/>
+      <c r="G386" s="11" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H386" s="11"/>
+      <c r="I386" s="11"/>
+      <c r="J386" s="11"/>
+      <c r="K386" s="11"/>
+      <c r="L386" s="11"/>
+      <c r="M386" s="11"/>
+      <c r="N386" s="11"/>
+      <c r="O386" s="11"/>
+    </row>
+    <row r="387" spans="1:15" ht="15">
+      <c r="A387" s="14"/>
+      <c r="B387" s="14" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C387" s="19" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D387" s="14"/>
+      <c r="E387" s="14"/>
+      <c r="F387" s="14"/>
+      <c r="G387" s="11" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H387" s="11"/>
+      <c r="I387" s="11"/>
+      <c r="J387" s="11"/>
+      <c r="K387" s="11"/>
+      <c r="L387" s="11"/>
+      <c r="M387" s="11"/>
+      <c r="N387" s="11"/>
+      <c r="O387" s="11"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="17" priority="1"/>

--- a/backend/dpd_.xlsx
+++ b/backend/dpd_.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="449" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0D6210D-4C47-406C-BB73-EDEF876CCF3C}"/>
+  <xr:revisionPtr revIDLastSave="471" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04E521BA-B54D-443D-9936-EC464FF802F0}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="1488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="1502">
   <si>
     <t>ACC</t>
   </si>
@@ -4479,7 +4479,7 @@
     <t>0862909636</t>
   </si>
   <si>
-    <t>นางดรุณี สงวนรัษฎ์</t>
+    <t>ดรุณี สงวนรัษฎ์</t>
   </si>
   <si>
     <t>0872063796</t>
@@ -4495,6 +4495,48 @@
   </si>
   <si>
     <t>พี่ดำ</t>
+  </si>
+  <si>
+    <t>สุนิศา เอียวงษ์</t>
+  </si>
+  <si>
+    <t>0935903969</t>
+  </si>
+  <si>
+    <t>ธิตติธร อ่อนวงษ์</t>
+  </si>
+  <si>
+    <t>0818847162</t>
+  </si>
+  <si>
+    <t>นลินี ดีตุ</t>
+  </si>
+  <si>
+    <t>0810391933</t>
+  </si>
+  <si>
+    <t>คำแพง เลิศลักษณ์สกุล</t>
+  </si>
+  <si>
+    <t>0862020650</t>
+  </si>
+  <si>
+    <t>ธัญพร หาคูณ</t>
+  </si>
+  <si>
+    <t>0815962456</t>
+  </si>
+  <si>
+    <t>เบญจวรรณ มีดี</t>
+  </si>
+  <si>
+    <t>0626791676</t>
+  </si>
+  <si>
+    <t>สุนทร ยอดรัก</t>
+  </si>
+  <si>
+    <t>0898566578</t>
   </si>
 </sst>
 </file>
@@ -5170,8 +5212,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O387" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="A1:O387" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O394" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
+  <autoFilter ref="A1:O394" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
   <tableColumns count="15">
     <tableColumn id="2" xr3:uid="{8056A4BF-1F51-408D-984A-13A9B55C81C2}" name="ACC" dataDxfId="14"/>
     <tableColumn id="1" xr3:uid="{AFEB8EFF-C7CD-487F-8B94-1A5CF9E8D70C}" name="NAME" dataDxfId="13"/>
@@ -5490,7 +5532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O387"/>
+  <dimension ref="A1:O394"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -17667,6 +17709,153 @@
       <c r="N387" s="11"/>
       <c r="O387" s="11"/>
     </row>
+    <row r="388" spans="1:15" ht="15">
+      <c r="A388" s="14"/>
+      <c r="B388" s="14" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C388" s="19" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D388" s="14"/>
+      <c r="E388" s="14"/>
+      <c r="F388" s="14"/>
+      <c r="G388" s="11"/>
+      <c r="H388" s="11"/>
+      <c r="I388" s="11"/>
+      <c r="J388" s="11"/>
+      <c r="K388" s="11"/>
+      <c r="L388" s="11"/>
+      <c r="M388" s="11"/>
+      <c r="N388" s="11"/>
+      <c r="O388" s="11"/>
+    </row>
+    <row r="389" spans="1:15" ht="15">
+      <c r="A389" s="14"/>
+      <c r="B389" s="14" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C389" s="19" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D389" s="14"/>
+      <c r="E389" s="14"/>
+      <c r="F389" s="14"/>
+      <c r="G389" s="11"/>
+      <c r="H389" s="11"/>
+      <c r="I389" s="11"/>
+      <c r="J389" s="11"/>
+      <c r="K389" s="11"/>
+      <c r="L389" s="11"/>
+      <c r="M389" s="11"/>
+      <c r="N389" s="11"/>
+      <c r="O389" s="11"/>
+    </row>
+    <row r="390" spans="1:15" ht="15">
+      <c r="A390" s="14"/>
+      <c r="B390" s="14" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C390" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D390" s="14"/>
+      <c r="E390" s="14"/>
+      <c r="F390" s="14"/>
+      <c r="G390" s="11"/>
+      <c r="H390" s="11"/>
+      <c r="I390" s="11"/>
+      <c r="J390" s="11"/>
+      <c r="K390" s="11"/>
+      <c r="L390" s="11"/>
+      <c r="M390" s="11"/>
+      <c r="N390" s="11"/>
+      <c r="O390" s="11"/>
+    </row>
+    <row r="391" spans="1:15" ht="15">
+      <c r="A391" s="14"/>
+      <c r="B391" s="14" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C391" s="19" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D391" s="14"/>
+      <c r="E391" s="14"/>
+      <c r="F391" s="14"/>
+      <c r="G391" s="11"/>
+      <c r="H391" s="11"/>
+      <c r="I391" s="11"/>
+      <c r="J391" s="11"/>
+      <c r="K391" s="11"/>
+      <c r="L391" s="11"/>
+      <c r="M391" s="11"/>
+      <c r="N391" s="11"/>
+      <c r="O391" s="11"/>
+    </row>
+    <row r="392" spans="1:15" ht="15">
+      <c r="A392" s="14"/>
+      <c r="B392" s="14" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C392" s="19" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D392" s="14"/>
+      <c r="E392" s="14"/>
+      <c r="F392" s="14"/>
+      <c r="G392" s="11"/>
+      <c r="H392" s="11"/>
+      <c r="I392" s="11"/>
+      <c r="J392" s="11"/>
+      <c r="K392" s="11"/>
+      <c r="L392" s="11"/>
+      <c r="M392" s="11"/>
+      <c r="N392" s="11"/>
+      <c r="O392" s="11"/>
+    </row>
+    <row r="393" spans="1:15" ht="15">
+      <c r="A393" s="14"/>
+      <c r="B393" s="14" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C393" s="19" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D393" s="14"/>
+      <c r="E393" s="14"/>
+      <c r="F393" s="14"/>
+      <c r="G393" s="11"/>
+      <c r="H393" s="11"/>
+      <c r="I393" s="11"/>
+      <c r="J393" s="11"/>
+      <c r="K393" s="11"/>
+      <c r="L393" s="11"/>
+      <c r="M393" s="11"/>
+      <c r="N393" s="11"/>
+      <c r="O393" s="11"/>
+    </row>
+    <row r="394" spans="1:15" ht="15">
+      <c r="A394" s="14"/>
+      <c r="B394" s="14" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C394" s="19" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D394" s="14"/>
+      <c r="E394" s="14"/>
+      <c r="F394" s="14"/>
+      <c r="G394" s="11"/>
+      <c r="H394" s="11"/>
+      <c r="I394" s="11"/>
+      <c r="J394" s="11"/>
+      <c r="K394" s="11"/>
+      <c r="L394" s="11"/>
+      <c r="M394" s="11"/>
+      <c r="N394" s="11"/>
+      <c r="O394" s="11"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="17" priority="1"/>

--- a/backend/dpd_.xlsx
+++ b/backend/dpd_.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="471" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04E521BA-B54D-443D-9936-EC464FF802F0}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{394AA7CE-1E94-4B4D-9F03-9480868BC37B}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="1502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="1518">
   <si>
     <t>ACC</t>
   </si>
@@ -4537,6 +4537,54 @@
   </si>
   <si>
     <t>0898566578</t>
+  </si>
+  <si>
+    <t>เนาวรัตน์ เจริญผล</t>
+  </si>
+  <si>
+    <t>0858761741</t>
+  </si>
+  <si>
+    <t>กัญภร อยู่พุ่ม</t>
+  </si>
+  <si>
+    <t>0899536569</t>
+  </si>
+  <si>
+    <t>พี่ี่จอย สองคอน</t>
+  </si>
+  <si>
+    <t>ขนิษฐา ผุยดา</t>
+  </si>
+  <si>
+    <t>0849511225</t>
+  </si>
+  <si>
+    <t>พี่ปู สองคอน</t>
+  </si>
+  <si>
+    <t>พิรมย์ ผุยดา</t>
+  </si>
+  <si>
+    <t>0980074360</t>
+  </si>
+  <si>
+    <t>ตรอ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> รัตนาภรณ์ ผุยดา </t>
+  </si>
+  <si>
+    <t>0813247442</t>
+  </si>
+  <si>
+    <t>อบต.สองห้อง</t>
+  </si>
+  <si>
+    <t>กุลภัทรณิชา ศรีวิลัย</t>
+  </si>
+  <si>
+    <t>0644564168</t>
   </si>
 </sst>
 </file>
@@ -5212,8 +5260,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O394" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="A1:O394" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O400" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
+  <autoFilter ref="A1:O400" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
   <tableColumns count="15">
     <tableColumn id="2" xr3:uid="{8056A4BF-1F51-408D-984A-13A9B55C81C2}" name="ACC" dataDxfId="14"/>
     <tableColumn id="1" xr3:uid="{AFEB8EFF-C7CD-487F-8B94-1A5CF9E8D70C}" name="NAME" dataDxfId="13"/>
@@ -5532,7 +5580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O394"/>
+  <dimension ref="A1:O400"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -17856,6 +17904,140 @@
       <c r="N394" s="11"/>
       <c r="O394" s="11"/>
     </row>
+    <row r="395" spans="1:15" ht="15">
+      <c r="A395" s="14"/>
+      <c r="B395" s="14" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C395" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D395" s="14"/>
+      <c r="E395" s="14"/>
+      <c r="F395" s="14"/>
+      <c r="G395" s="11"/>
+      <c r="H395" s="11"/>
+      <c r="I395" s="11"/>
+      <c r="J395" s="11"/>
+      <c r="K395" s="11"/>
+      <c r="L395" s="11"/>
+      <c r="M395" s="11"/>
+      <c r="N395" s="11"/>
+      <c r="O395" s="11"/>
+    </row>
+    <row r="396" spans="1:15" ht="15">
+      <c r="A396" s="14"/>
+      <c r="B396" s="14" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C396" s="19" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D396" s="14"/>
+      <c r="E396" s="14"/>
+      <c r="F396" s="14"/>
+      <c r="G396" s="11" t="s">
+        <v>1506</v>
+      </c>
+      <c r="H396" s="11"/>
+      <c r="I396" s="11"/>
+      <c r="J396" s="11"/>
+      <c r="K396" s="11"/>
+      <c r="L396" s="11"/>
+      <c r="M396" s="11"/>
+      <c r="N396" s="11"/>
+      <c r="O396" s="11"/>
+    </row>
+    <row r="397" spans="1:15" ht="15">
+      <c r="A397" s="14"/>
+      <c r="B397" s="14" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C397" s="19" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D397" s="14"/>
+      <c r="E397" s="14"/>
+      <c r="F397" s="14"/>
+      <c r="G397" s="11" t="s">
+        <v>1509</v>
+      </c>
+      <c r="H397" s="11"/>
+      <c r="I397" s="11"/>
+      <c r="J397" s="11"/>
+      <c r="K397" s="11"/>
+      <c r="L397" s="11"/>
+      <c r="M397" s="11"/>
+      <c r="N397" s="11"/>
+      <c r="O397" s="11"/>
+    </row>
+    <row r="398" spans="1:15" ht="15">
+      <c r="A398" s="14"/>
+      <c r="B398" s="14" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C398" s="19" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D398" s="14"/>
+      <c r="E398" s="14"/>
+      <c r="F398" s="14"/>
+      <c r="G398" s="11" t="s">
+        <v>1512</v>
+      </c>
+      <c r="H398" s="11"/>
+      <c r="I398" s="11"/>
+      <c r="J398" s="11"/>
+      <c r="K398" s="11"/>
+      <c r="L398" s="11"/>
+      <c r="M398" s="11"/>
+      <c r="N398" s="11"/>
+      <c r="O398" s="11"/>
+    </row>
+    <row r="399" spans="1:15" ht="15">
+      <c r="A399" s="14"/>
+      <c r="B399" s="14" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C399" s="19" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D399" s="14"/>
+      <c r="E399" s="14"/>
+      <c r="F399" s="14"/>
+      <c r="G399" s="11" t="s">
+        <v>1515</v>
+      </c>
+      <c r="H399" s="11"/>
+      <c r="I399" s="11"/>
+      <c r="J399" s="11"/>
+      <c r="K399" s="11"/>
+      <c r="L399" s="11"/>
+      <c r="M399" s="11"/>
+      <c r="N399" s="11"/>
+      <c r="O399" s="11"/>
+    </row>
+    <row r="400" spans="1:15" ht="15">
+      <c r="A400" s="14"/>
+      <c r="B400" s="14" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C400" s="19" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D400" s="14"/>
+      <c r="E400" s="14"/>
+      <c r="F400" s="14"/>
+      <c r="G400" s="11"/>
+      <c r="H400" s="11"/>
+      <c r="I400" s="11"/>
+      <c r="J400" s="11"/>
+      <c r="K400" s="11"/>
+      <c r="L400" s="11"/>
+      <c r="M400" s="11"/>
+      <c r="N400" s="11"/>
+      <c r="O400" s="11"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="17" priority="1"/>

--- a/backend/dpd_.xlsx
+++ b/backend/dpd_.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="490" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{394AA7CE-1E94-4B4D-9F03-9480868BC37B}"/>
+  <xr:revisionPtr revIDLastSave="497" documentId="11_C380EA0251C7A0836B02CE998F2F241A78A18387" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8B53748-784C-4ABF-B6B6-952177C7F736}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="1524">
   <si>
     <t>ACC</t>
   </si>
@@ -4095,7 +4095,7 @@
     <t>ศรีจันทร์ อุตยะราช</t>
   </si>
   <si>
-    <t>0928086920</t>
+    <t>0861199105</t>
   </si>
   <si>
     <t>d6b80564-61ca-44cf-b8c2-c82532314920</t>
@@ -4585,6 +4585,24 @@
   </si>
   <si>
     <t>0644564168</t>
+  </si>
+  <si>
+    <t>สมชาติ พุฒลา</t>
+  </si>
+  <si>
+    <t>0979686435</t>
+  </si>
+  <si>
+    <t>ประเดิมศักดิ์ ปิตุภูมิสวัสดิ์</t>
+  </si>
+  <si>
+    <t>0947451553</t>
+  </si>
+  <si>
+    <t>สมชาติ ฟุ้งสมุทร</t>
+  </si>
+  <si>
+    <t>0615424655</t>
   </si>
 </sst>
 </file>
@@ -4757,7 +4775,7 @@
     <xf numFmtId="11" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
@@ -5260,8 +5278,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O400" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="A1:O400" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}" name="Table2" displayName="Table2" ref="A1:O403" totalsRowShown="0" dataDxfId="16" tableBorderDxfId="15">
+  <autoFilter ref="A1:O403" xr:uid="{72E25134-A5A7-4DE0-A267-189B525B70EA}"/>
   <tableColumns count="15">
     <tableColumn id="2" xr3:uid="{8056A4BF-1F51-408D-984A-13A9B55C81C2}" name="ACC" dataDxfId="14"/>
     <tableColumn id="1" xr3:uid="{AFEB8EFF-C7CD-487F-8B94-1A5CF9E8D70C}" name="NAME" dataDxfId="13"/>
@@ -5580,7 +5598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O400"/>
+  <dimension ref="A1:O403"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -18038,6 +18056,69 @@
       <c r="N400" s="11"/>
       <c r="O400" s="11"/>
     </row>
+    <row r="401" spans="1:15" ht="15">
+      <c r="A401" s="14"/>
+      <c r="B401" s="14" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C401" s="19" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D401" s="14"/>
+      <c r="E401" s="14"/>
+      <c r="F401" s="14"/>
+      <c r="G401" s="11"/>
+      <c r="H401" s="11"/>
+      <c r="I401" s="11"/>
+      <c r="J401" s="11"/>
+      <c r="K401" s="11"/>
+      <c r="L401" s="11"/>
+      <c r="M401" s="11"/>
+      <c r="N401" s="11"/>
+      <c r="O401" s="11"/>
+    </row>
+    <row r="402" spans="1:15" ht="15">
+      <c r="A402" s="14"/>
+      <c r="B402" s="14" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C402" s="19" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="11"/>
+      <c r="H402" s="11"/>
+      <c r="I402" s="11"/>
+      <c r="J402" s="11"/>
+      <c r="K402" s="11"/>
+      <c r="L402" s="11"/>
+      <c r="M402" s="11"/>
+      <c r="N402" s="11"/>
+      <c r="O402" s="11"/>
+    </row>
+    <row r="403" spans="1:15" ht="15">
+      <c r="A403" s="14"/>
+      <c r="B403" s="14" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C403" s="19" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="11"/>
+      <c r="H403" s="11"/>
+      <c r="I403" s="11"/>
+      <c r="J403" s="11"/>
+      <c r="K403" s="11"/>
+      <c r="L403" s="11"/>
+      <c r="M403" s="11"/>
+      <c r="N403" s="11"/>
+      <c r="O403" s="11"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="17" priority="1"/>
